--- a/data/trans_camb/P2B_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P2B_R-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>20,38; 48,45</t>
+          <t>19,86; 49,19</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>16,72; 48,63</t>
+          <t>16,76; 49,24</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-15,77; 23,37</t>
+          <t>-14,62; 25,96</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>46,47; 70,7</t>
+          <t>44,72; 69,6</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>34,23; 64,2</t>
+          <t>34,85; 63,94</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 26,8</t>
+          <t>-0,95; 27,07</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>36,6; 56,03</t>
+          <t>36,64; 55,85</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>31,26; 52,54</t>
+          <t>31,83; 53,6</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-4,14; 21,7</t>
+          <t>-3,75; 20,35</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>47,05; 177,27</t>
+          <t>42,74; 172,97</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>37,05; 162,05</t>
+          <t>41,07; 181,51</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-38,21; 77,81</t>
+          <t>-34,42; 84,02</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>134,92; 424,08</t>
+          <t>124,66; 409,32</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>95,07; 345,17</t>
+          <t>102,71; 371,91</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 139,51</t>
+          <t>-5,49; 142,7</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>97,09; 223,25</t>
+          <t>96,34; 228,61</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>82,84; 203,5</t>
+          <t>81,53; 205,07</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-11,88; 80,53</t>
+          <t>-10,37; 78,22</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>49,77; 60,79</t>
+          <t>49,24; 59,94</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>33,07; 44,65</t>
+          <t>33,54; 45,25</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 9,37</t>
+          <t>-3,94; 9,9</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>49,52; 59,55</t>
+          <t>49,32; 59,24</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>31,5; 43,2</t>
+          <t>31,78; 42,57</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,26; 14,24</t>
+          <t>1,87; 14,73</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>51,01; 58,59</t>
+          <t>51,3; 58,36</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>34,64; 42,55</t>
+          <t>34,11; 42,15</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,82; 9,66</t>
+          <t>1,25; 10,46</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>154,46; 247,86</t>
+          <t>150,33; 237,43</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>101,02; 177,9</t>
+          <t>105,6; 182,72</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-11,88; 35,81</t>
+          <t>-11,94; 38,38</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>149,65; 232,79</t>
+          <t>150,72; 230,5</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>97,14; 164,94</t>
+          <t>97,94; 161,81</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,78; 52,67</t>
+          <t>5,37; 53,66</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>161,52; 223,18</t>
+          <t>161,98; 219,33</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>109,7; 159,82</t>
+          <t>109,36; 158,08</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,08; 35,79</t>
+          <t>4,14; 37,99</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>39,53; 56,94</t>
+          <t>39,72; 56,82</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>22,52; 41,18</t>
+          <t>21,14; 40,43</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-19,9; -2,54</t>
+          <t>-20,16; -2,94</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>38,64; 55,92</t>
+          <t>39,15; 56,74</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>30,94; 50,3</t>
+          <t>32,27; 50,01</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-17,97; -0,07</t>
+          <t>-18,24; -0,05</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>41,55; 53,7</t>
+          <t>41,95; 54,06</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>29,42; 42,84</t>
+          <t>29,48; 42,49</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-17,17; -4,58</t>
+          <t>-17,22; -4,8</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>95,05; 187,41</t>
+          <t>94,3; 186,92</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>54,83; 131,43</t>
+          <t>50,93; 130,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-49,39; -8,4</t>
+          <t>-49,7; -8,47</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>94,09; 197,53</t>
+          <t>98,42; 203,72</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>76,12; 177,77</t>
+          <t>79,79; 170,71</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-46,06; -0,16</t>
+          <t>-47,07; -0,97</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>105,63; 172,09</t>
+          <t>104,16; 171,52</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>74,35; 136,76</t>
+          <t>74,89; 133,34</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-43,56; -13,91</t>
+          <t>-44,94; -14,06</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>46,51; 55,17</t>
+          <t>46,57; 55,47</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>31,47; 40,94</t>
+          <t>31,62; 41,35</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-6,26; 4,42</t>
+          <t>-6,85; 4,21</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>49,08; 57,45</t>
+          <t>48,94; 57,36</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>34,91; 43,83</t>
+          <t>34,55; 44,17</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 9,47</t>
+          <t>-0,74; 8,84</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>49,15; 55,11</t>
+          <t>49,2; 55,04</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>34,83; 41,33</t>
+          <t>34,7; 41,13</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 5,44</t>
+          <t>-1,88; 5,41</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>134,61; 191,51</t>
+          <t>132,73; 193,69</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>91,9; 141,24</t>
+          <t>91,34; 144,81</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-18,7; 14,74</t>
+          <t>-19,51; 13,94</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>147,63; 211,23</t>
+          <t>147,56; 210,6</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>106,73; 158,7</t>
+          <t>105,35; 160,46</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 33,79</t>
+          <t>-1,94; 31,66</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>150,17; 191,79</t>
+          <t>148,36; 189,84</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>106,02; 143,69</t>
+          <t>104,85; 141,51</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-4,51; 18,65</t>
+          <t>-5,76; 18,22</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2B_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P2B_R-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>19,86; 49,19</t>
+          <t>19,98; 48,42</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>16,76; 49,24</t>
+          <t>17,29; 48,93</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-14,62; 25,96</t>
+          <t>-14,18; 24,13</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>44,72; 69,6</t>
+          <t>45,43; 70,18</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>34,85; 63,94</t>
+          <t>36,33; 63,37</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 27,07</t>
+          <t>-1,62; 27,36</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>36,64; 55,85</t>
+          <t>36,39; 56,42</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>31,83; 53,6</t>
+          <t>31,63; 54,11</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 20,35</t>
+          <t>-3,04; 19,86</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>42,74; 172,97</t>
+          <t>45,7; 176,29</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>41,07; 181,51</t>
+          <t>37,86; 173,07</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-34,42; 84,02</t>
+          <t>-35,61; 92,14</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>124,66; 409,32</t>
+          <t>123,1; 381,34</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>102,71; 371,91</t>
+          <t>104,61; 348,95</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-5,49; 142,7</t>
+          <t>-5,66; 137,58</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>96,34; 228,61</t>
+          <t>95,28; 222,53</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>81,53; 205,07</t>
+          <t>83,98; 211,81</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-10,37; 78,22</t>
+          <t>-8,75; 72,73</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>49,24; 59,94</t>
+          <t>49,43; 60,37</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>33,54; 45,25</t>
+          <t>33,71; 45,05</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,94; 9,9</t>
+          <t>-4,18; 9,4</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>49,32; 59,24</t>
+          <t>49,25; 59,55</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>31,78; 42,57</t>
+          <t>31,87; 43,4</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,87; 14,73</t>
+          <t>1,76; 14,22</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>51,3; 58,36</t>
+          <t>50,67; 58,24</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>34,11; 42,15</t>
+          <t>34,08; 42,17</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,25; 10,46</t>
+          <t>1,53; 9,81</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>150,33; 237,43</t>
+          <t>153,73; 246,89</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>105,6; 182,72</t>
+          <t>106,07; 181,77</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-11,94; 38,38</t>
+          <t>-12,26; 36,7</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>150,72; 230,5</t>
+          <t>150,02; 233,19</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>97,94; 161,81</t>
+          <t>97,81; 168,34</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,37; 53,66</t>
+          <t>5,66; 53,59</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>161,98; 219,33</t>
+          <t>160,16; 218,87</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>109,36; 158,08</t>
+          <t>109,61; 158,14</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,14; 37,99</t>
+          <t>5,18; 35,98</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>39,72; 56,82</t>
+          <t>39,35; 56,89</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>21,14; 40,43</t>
+          <t>21,72; 40,56</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-20,16; -2,94</t>
+          <t>-21,37; -3,39</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>39,15; 56,74</t>
+          <t>39,13; 55,91</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>32,27; 50,01</t>
+          <t>31,16; 49,24</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-18,24; -0,05</t>
+          <t>-18,57; -0,89</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>41,95; 54,06</t>
+          <t>41,55; 54,31</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>29,48; 42,49</t>
+          <t>29,37; 42,35</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-17,22; -4,8</t>
+          <t>-17,08; -4,53</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>94,3; 186,92</t>
+          <t>91,22; 186,2</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>50,93; 130,0</t>
+          <t>51,26; 131,05</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-49,7; -8,47</t>
+          <t>-51,56; -9,94</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>98,42; 203,72</t>
+          <t>95,65; 196,36</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>79,79; 170,71</t>
+          <t>76,7; 169,15</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-47,07; -0,97</t>
+          <t>-45,87; -2,09</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>104,16; 171,52</t>
+          <t>104,62; 172,52</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>74,89; 133,34</t>
+          <t>73,91; 134,34</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-44,94; -14,06</t>
+          <t>-44,16; -13,22</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>46,57; 55,47</t>
+          <t>46,41; 55,89</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>31,62; 41,35</t>
+          <t>31,65; 41,27</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-6,85; 4,21</t>
+          <t>-6,11; 4,55</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>48,94; 57,36</t>
+          <t>49,61; 57,63</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>34,55; 44,17</t>
+          <t>34,79; 43,89</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 8,84</t>
+          <t>-0,65; 8,85</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>49,2; 55,04</t>
+          <t>49,4; 55,03</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>34,7; 41,13</t>
+          <t>34,92; 41,77</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 5,41</t>
+          <t>-1,68; 5,57</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>132,73; 193,69</t>
+          <t>134,55; 195,41</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>91,34; 144,81</t>
+          <t>89,73; 141,25</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-19,51; 13,94</t>
+          <t>-17,97; 15,72</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>147,56; 210,6</t>
+          <t>148,1; 207,39</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>105,35; 160,46</t>
+          <t>107,23; 158,95</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 31,66</t>
+          <t>-2,1; 31,79</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>148,36; 189,84</t>
+          <t>149,52; 190,04</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>104,85; 141,51</t>
+          <t>106,43; 144,43</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-5,76; 18,22</t>
+          <t>-5,04; 19,29</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2B_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P2B_R-Estudios-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>58,85</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>51,2</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>14,99</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>34,6</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>32,99</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2,05</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>58,85</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>51,2</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,93</t>
+          <t>0,3</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>7,77</t>
+          <t>7,58</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>19,98; 48,42</t>
+          <t>46,47; 70,7</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>17,29; 48,93</t>
+          <t>34,23; 64,2</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-14,18; 24,13</t>
+          <t>0,14; 28,1</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>45,43; 70,18</t>
+          <t>20,38; 48,45</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>36,33; 63,37</t>
+          <t>16,72; 48,63</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 27,36</t>
+          <t>-15,25; 16,78</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>36,39; 56,42</t>
+          <t>36,6; 56,03</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>31,63; 54,11</t>
+          <t>31,26; 52,54</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 19,86</t>
+          <t>-2,77; 19,47</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>225,99%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>196,64%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>57,55%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>94,18%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>89,81%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>5,58%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>225,99%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>196,64%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>53,49%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>23,96%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>45,7; 176,29</t>
+          <t>134,92; 424,08</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>37,86; 173,07</t>
+          <t>95,07; 345,17</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-35,61; 92,14</t>
+          <t>0,69; 145,16</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>123,1; 381,34</t>
+          <t>47,05; 177,27</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>104,61; 348,95</t>
+          <t>37,05; 162,05</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-5,66; 137,58</t>
+          <t>-35,9; 58,98</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>95,28; 222,53</t>
+          <t>97,09; 223,25</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>83,98; 211,81</t>
+          <t>82,84; 203,5</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-8,75; 72,73</t>
+          <t>-7,2; 73,29</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>54,54</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>37,21</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>8,61</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>55,16</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>39,36</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>3,64</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>54,54</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>37,21</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,61</t>
+          <t>6,08</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>5,74</t>
+          <t>7,4</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>49,43; 60,37</t>
+          <t>49,52; 59,55</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>33,71; 45,05</t>
+          <t>31,5; 43,2</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,18; 9,4</t>
+          <t>3,18; 14,95</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>49,25; 59,55</t>
+          <t>49,77; 60,79</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>31,87; 43,4</t>
+          <t>33,07; 44,65</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,76; 14,22</t>
+          <t>1,0; 12,25</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>50,67; 58,24</t>
+          <t>51,01; 58,59</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>34,08; 42,17</t>
+          <t>34,64; 42,55</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,53; 9,81</t>
+          <t>3,27; 11,35</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>185,76%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>126,74%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>29,31%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>193,87%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>138,32%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>12,81%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>185,76%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>126,74%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>25,56%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>153,73; 246,89</t>
+          <t>149,65; 232,79</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>106,07; 181,77</t>
+          <t>97,14; 164,94</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-12,26; 36,7</t>
+          <t>10,01; 57,27</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>150,02; 233,19</t>
+          <t>154,46; 247,86</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>97,81; 168,34</t>
+          <t>101,02; 177,9</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,66; 53,59</t>
+          <t>2,93; 47,65</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>160,16; 218,87</t>
+          <t>161,52; 223,18</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>109,61; 158,14</t>
+          <t>109,7; 159,82</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,18; 35,98</t>
+          <t>10,64; 42,06</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>47,54</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>40,95</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-8,45</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>48,5</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>31,34</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-12,28</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>47,54</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>40,95</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-9,48</t>
+          <t>-12,69</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-10,89</t>
+          <t>-10,56</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>39,35; 56,89</t>
+          <t>38,64; 55,92</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>21,72; 40,56</t>
+          <t>30,94; 50,3</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-21,37; -3,39</t>
+          <t>-17,13; 1,26</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>39,13; 55,91</t>
+          <t>39,53; 56,94</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>31,16; 49,24</t>
+          <t>22,52; 41,18</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-18,57; -0,89</t>
+          <t>-20,3; -2,75</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>41,55; 54,31</t>
+          <t>41,55; 53,7</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>29,37; 42,35</t>
+          <t>29,42; 42,84</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-17,08; -4,53</t>
+          <t>-16,89; -4,11</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>137,1%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>118,1%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-24,36%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>132,34%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>85,51%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-33,49%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>137,1%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>118,1%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-27,33%</t>
+          <t>-34,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-30,48%</t>
+          <t>-29,56%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>91,22; 186,2</t>
+          <t>94,09; 197,53</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>51,26; 131,05</t>
+          <t>76,12; 177,77</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-51,56; -9,94</t>
+          <t>-43,51; 5,71</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>95,65; 196,36</t>
+          <t>95,05; 187,41</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>76,7; 169,15</t>
+          <t>54,83; 131,43</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-45,87; -2,09</t>
+          <t>-50,44; -9,2</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>104,62; 172,52</t>
+          <t>105,63; 172,09</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>73,91; 134,34</t>
+          <t>74,35; 136,76</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-44,16; -13,22</t>
+          <t>-43,11; -13,11</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>53,3</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>39,45</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>5,12</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>50,96</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>36,4</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-0,69</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>53,3</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>39,45</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,11</t>
+          <t>0,59</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1,84</t>
+          <t>2,96</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>46,41; 55,89</t>
+          <t>49,08; 57,45</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>31,65; 41,27</t>
+          <t>34,91; 43,83</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-6,11; 4,55</t>
+          <t>0,54; 10,19</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>49,61; 57,63</t>
+          <t>46,51; 55,17</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>34,79; 43,89</t>
+          <t>31,47; 40,94</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 8,85</t>
+          <t>-4,2; 4,97</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>49,4; 55,03</t>
+          <t>49,15; 55,11</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>34,92; 41,77</t>
+          <t>34,83; 41,33</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 5,57</t>
+          <t>-0,15; 6,4</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>176,04%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>130,28%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>16,92%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>161,23%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>115,17%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-2,2%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>176,04%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>130,28%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>9,57%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>134,55; 195,41</t>
+          <t>147,63; 211,23</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>89,73; 141,25</t>
+          <t>106,73; 158,7</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-17,97; 15,72</t>
+          <t>1,64; 37,37</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>148,1; 207,39</t>
+          <t>134,61; 191,51</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>107,23; 158,95</t>
+          <t>91,9; 141,24</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 31,79</t>
+          <t>-12,42; 16,84</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>149,52; 190,04</t>
+          <t>150,17; 191,79</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>106,43; 144,43</t>
+          <t>106,02; 143,69</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-5,04; 19,29</t>
+          <t>-0,44; 21,94</t>
         </is>
       </c>
     </row>
